--- a/source/data/t1-readme-metadata-2025.xlsx
+++ b/source/data/t1-readme-metadata-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pxn045\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363731DA-87CD-41BB-95BE-7F9FEDEC0172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363B2A61-DBEF-4EAC-8899-5F7981B235A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3031,9 +3031,6 @@
     <t xml:space="preserve">Opp Title </t>
   </si>
   <si>
-    <t>New EN description</t>
-  </si>
-  <si>
     <t>New EN Title/H1 (must fit for last 10 years?)</t>
   </si>
   <si>
@@ -3047,6 +3044,9 @@
   </si>
   <si>
     <t>New EN keywords</t>
+  </si>
+  <si>
+    <t>New EN Intro (description)</t>
   </si>
 </sst>
 </file>
@@ -3313,19 +3313,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>7</v>
@@ -3337,19 +3337,19 @@
         <v>1000</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="71.25">
